--- a/Assets/Resources/CSV/LootTables.xlsx
+++ b/Assets/Resources/CSV/LootTables.xlsx
@@ -1,46 +1,263 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UNITY GAME\类银河恶魔城\Assets\Resources\CSV\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF71BBA5-464B-475A-8975-F09B5167EB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="73">
+  <si>
+    <t>rowId</t>
+  </si>
+  <si>
+    <t>tableId</t>
+  </si>
+  <si>
+    <t>tableName</t>
+  </si>
+  <si>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>itemName</t>
+  </si>
+  <si>
+    <t>dropChance</t>
+  </si>
+  <si>
+    <t>minCount</t>
+  </si>
+  <si>
+    <t>maxCount</t>
+  </si>
+  <si>
+    <t>T001</t>
+  </si>
+  <si>
+    <t>LootTable - 血瓶</t>
+  </si>
+  <si>
+    <t>小回春</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>血瓶1</t>
+  </si>
+  <si>
+    <t>小回春1</t>
+  </si>
+  <si>
+    <t>血瓶</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>LootTable -新手装备</t>
+  </si>
+  <si>
+    <t>木剑</t>
+  </si>
+  <si>
+    <t>皮兜帽</t>
+  </si>
+  <si>
+    <t>皮手套</t>
+  </si>
+  <si>
+    <t>皮甲</t>
+  </si>
+  <si>
+    <t>皮靴</t>
+  </si>
+  <si>
+    <t>T003</t>
+  </si>
+  <si>
+    <t>LootTable -新手装备——骷髅掉落</t>
+  </si>
+  <si>
+    <t>T004</t>
+  </si>
+  <si>
+    <t>LootTable - 铜掉落池</t>
+  </si>
+  <si>
+    <t>铜矿石</t>
+  </si>
+  <si>
+    <t>铜盔</t>
+  </si>
+  <si>
+    <t>铜甲</t>
+  </si>
+  <si>
+    <t>铜靴</t>
+  </si>
+  <si>
+    <t>铜手套</t>
+  </si>
+  <si>
+    <t>铜剑</t>
+  </si>
+  <si>
+    <t>铜项链</t>
+  </si>
+  <si>
+    <t>铜手镯</t>
+  </si>
+  <si>
+    <t>铜戒指</t>
+  </si>
+  <si>
+    <t>T005</t>
+  </si>
+  <si>
+    <t>LootTable - 铁掉落池</t>
+  </si>
+  <si>
+    <t>铁矿石</t>
+  </si>
+  <si>
+    <t>铁盔</t>
+  </si>
+  <si>
+    <t>铁甲</t>
+  </si>
+  <si>
+    <t>铁靴</t>
+  </si>
+  <si>
+    <t>铁手套</t>
+  </si>
+  <si>
+    <t>铁剑</t>
+  </si>
+  <si>
+    <t>铁项链</t>
+  </si>
+  <si>
+    <t>铁手镯</t>
+  </si>
+  <si>
+    <t>铁戒指</t>
+  </si>
+  <si>
+    <t>T006</t>
+  </si>
+  <si>
+    <t>LootTable - 金掉落池</t>
+  </si>
+  <si>
+    <t>金矿石</t>
+  </si>
+  <si>
+    <t>金盔</t>
+  </si>
+  <si>
+    <t>金甲</t>
+  </si>
+  <si>
+    <t>金靴</t>
+  </si>
+  <si>
+    <t>金手套</t>
+  </si>
+  <si>
+    <t>金剑</t>
+  </si>
+  <si>
+    <t>金项链</t>
+  </si>
+  <si>
+    <t>金手镯</t>
+  </si>
+  <si>
+    <t>金戒指</t>
+  </si>
+  <si>
+    <t>T007</t>
+  </si>
+  <si>
+    <t>LootTable - 钻石掉落池</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>钻石盔</t>
+  </si>
+  <si>
+    <t>钻石甲</t>
+  </si>
+  <si>
+    <t>钻石靴</t>
+  </si>
+  <si>
+    <t>钻石手套</t>
+  </si>
+  <si>
+    <t>钻石剑</t>
+  </si>
+  <si>
+    <t>钻石项链</t>
+  </si>
+  <si>
+    <t>钻石手镯</t>
+  </si>
+  <si>
+    <t>钻石戒指</t>
+  </si>
+  <si>
+    <t>T008</t>
+  </si>
+  <si>
+    <t>LootTable - 传说掉落池</t>
+  </si>
+  <si>
+    <t>传说之刃</t>
+  </si>
+  <si>
+    <t>远古龙鳞甲</t>
+  </si>
+  <si>
+    <t>currencyAmount</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,18 +282,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -86,44 +311,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -151,14 +376,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -186,6 +428,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -197,180 +456,136 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -392,64 +607,73 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I53"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="28.875" customWidth="1"/>
+    <col min="4" max="4" width="8.875" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="8" width="8.875" customWidth="1"/>
+    <col min="9" max="9" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>rowId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>tableId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>tableName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>itemId</v>
-      </c>
-      <c r="E1" t="str">
-        <v>itemName</v>
-      </c>
-      <c r="F1" t="str">
-        <v>dropChance</v>
-      </c>
-      <c r="G1" t="str">
-        <v>minCount</v>
-      </c>
-      <c r="H1" t="str">
-        <v>maxCount</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>400001</v>
       </c>
-      <c r="B2" t="str">
-        <v>T001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>LootTable - 血瓶</v>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2">
         <v>120001</v>
       </c>
-      <c r="E2" t="str">
-        <v>小回春</v>
+      <c r="E2" t="s">
+        <v>10</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -460,22 +684,25 @@
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>400002</v>
       </c>
-      <c r="B3" t="str">
-        <v>T001</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
       </c>
       <c r="D3">
         <v>120004</v>
       </c>
-      <c r="E3" t="str">
-        <v>血瓶1</v>
+      <c r="E3" t="s">
+        <v>12</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -487,21 +714,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>400003</v>
       </c>
-      <c r="B4" t="str">
-        <v>T001</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
         <v>120002</v>
       </c>
-      <c r="E4" t="str">
-        <v>小回春1</v>
+      <c r="E4" t="s">
+        <v>13</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -513,21 +740,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>400004</v>
       </c>
-      <c r="B5" t="str">
-        <v>T001</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
       <c r="D5">
         <v>120003</v>
       </c>
-      <c r="E5" t="str">
-        <v>血瓶</v>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -539,21 +766,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>400005</v>
       </c>
-      <c r="B6" t="str">
-        <v>T002</v>
-      </c>
-      <c r="C6" t="str">
-        <v>LootTable -新手装备</v>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
       </c>
       <c r="D6">
         <v>100101</v>
       </c>
-      <c r="E6" t="str">
-        <v>木剑</v>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -564,22 +791,25 @@
       <c r="H6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>400006</v>
       </c>
-      <c r="B7" t="str">
-        <v>T002</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
       </c>
       <c r="D7">
         <v>110101</v>
       </c>
-      <c r="E7" t="str">
-        <v>皮兜帽</v>
+      <c r="E7" t="s">
+        <v>18</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -591,21 +821,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>400007</v>
       </c>
-      <c r="B8" t="str">
-        <v>T002</v>
-      </c>
-      <c r="C8" t="str">
-        <v/>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
       <c r="D8">
         <v>110401</v>
       </c>
-      <c r="E8" t="str">
-        <v>皮手套</v>
+      <c r="E8" t="s">
+        <v>19</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -617,21 +847,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>400008</v>
       </c>
-      <c r="B9" t="str">
-        <v>T002</v>
-      </c>
-      <c r="C9" t="str">
-        <v/>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
       </c>
       <c r="D9">
         <v>110201</v>
       </c>
-      <c r="E9" t="str">
-        <v>皮甲</v>
+      <c r="E9" t="s">
+        <v>20</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -643,21 +873,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>400009</v>
       </c>
-      <c r="B10" t="str">
-        <v>T002</v>
-      </c>
-      <c r="C10" t="str">
-        <v/>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
       </c>
       <c r="D10">
         <v>110301</v>
       </c>
-      <c r="E10" t="str">
-        <v>皮靴</v>
+      <c r="E10" t="s">
+        <v>21</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -669,21 +899,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>400010</v>
       </c>
-      <c r="B11" t="str">
-        <v>T003</v>
-      </c>
-      <c r="C11" t="str">
-        <v>LootTable -新手装备——骷髅掉落</v>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
       </c>
       <c r="D11">
         <v>100101</v>
       </c>
-      <c r="E11" t="str">
-        <v>木剑</v>
+      <c r="E11" t="s">
+        <v>17</v>
       </c>
       <c r="F11">
         <v>20</v>
@@ -694,22 +924,25 @@
       <c r="H11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="I11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>400011</v>
       </c>
-      <c r="B12" t="str">
-        <v>T003</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
       </c>
       <c r="D12">
         <v>110101</v>
       </c>
-      <c r="E12" t="str">
-        <v>皮兜帽</v>
+      <c r="E12" t="s">
+        <v>18</v>
       </c>
       <c r="F12">
         <v>20</v>
@@ -721,21 +954,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>400012</v>
       </c>
-      <c r="B13" t="str">
-        <v>T003</v>
-      </c>
-      <c r="C13" t="str">
-        <v/>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
       </c>
       <c r="D13">
         <v>110401</v>
       </c>
-      <c r="E13" t="str">
-        <v>皮手套</v>
+      <c r="E13" t="s">
+        <v>19</v>
       </c>
       <c r="F13">
         <v>20</v>
@@ -747,21 +980,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>400013</v>
       </c>
-      <c r="B14" t="str">
-        <v>T003</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
       </c>
       <c r="D14">
         <v>110201</v>
       </c>
-      <c r="E14" t="str">
-        <v>皮甲</v>
+      <c r="E14" t="s">
+        <v>20</v>
       </c>
       <c r="F14">
         <v>20</v>
@@ -773,21 +1006,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>400014</v>
       </c>
-      <c r="B15" t="str">
-        <v>T003</v>
-      </c>
-      <c r="C15" t="str">
-        <v/>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
       </c>
       <c r="D15">
         <v>110301</v>
       </c>
-      <c r="E15" t="str">
-        <v>皮靴</v>
+      <c r="E15" t="s">
+        <v>21</v>
       </c>
       <c r="F15">
         <v>20</v>
@@ -799,21 +1032,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>400015</v>
       </c>
-      <c r="B16" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C16" t="str">
-        <v>LootTable - 铜掉落池</v>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
       </c>
       <c r="D16">
         <v>130004</v>
       </c>
-      <c r="E16" t="str">
-        <v>铜矿石</v>
+      <c r="E16" t="s">
+        <v>26</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -824,22 +1057,25 @@
       <c r="H16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="I16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>400016</v>
       </c>
-      <c r="B17" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C17" t="str">
-        <v/>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
       </c>
       <c r="D17">
         <v>110103</v>
       </c>
-      <c r="E17" t="str">
-        <v>铜盔</v>
+      <c r="E17" t="s">
+        <v>27</v>
       </c>
       <c r="F17">
         <v>30</v>
@@ -851,21 +1087,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>400017</v>
       </c>
-      <c r="B18" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C18" t="str">
-        <v/>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
       </c>
       <c r="D18">
         <v>110203</v>
       </c>
-      <c r="E18" t="str">
-        <v>铜甲</v>
+      <c r="E18" t="s">
+        <v>28</v>
       </c>
       <c r="F18">
         <v>30</v>
@@ -877,21 +1113,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>400018</v>
       </c>
-      <c r="B19" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C19" t="str">
-        <v/>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
       </c>
       <c r="D19">
         <v>110303</v>
       </c>
-      <c r="E19" t="str">
-        <v>铜靴</v>
+      <c r="E19" t="s">
+        <v>29</v>
       </c>
       <c r="F19">
         <v>30</v>
@@ -903,21 +1139,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>400019</v>
       </c>
-      <c r="B20" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C20" t="str">
-        <v/>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
       </c>
       <c r="D20">
         <v>110403</v>
       </c>
-      <c r="E20" t="str">
-        <v>铜手套</v>
+      <c r="E20" t="s">
+        <v>30</v>
       </c>
       <c r="F20">
         <v>30</v>
@@ -929,21 +1165,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>400020</v>
       </c>
-      <c r="B21" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C21" t="str">
-        <v/>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
       </c>
       <c r="D21">
         <v>100103</v>
       </c>
-      <c r="E21" t="str">
-        <v>铜剑</v>
+      <c r="E21" t="s">
+        <v>31</v>
       </c>
       <c r="F21">
         <v>30</v>
@@ -955,21 +1191,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>400021</v>
       </c>
-      <c r="B22" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
       </c>
       <c r="D22">
         <v>110506</v>
       </c>
-      <c r="E22" t="str">
-        <v>铜项链</v>
+      <c r="E22" t="s">
+        <v>32</v>
       </c>
       <c r="F22">
         <v>20</v>
@@ -981,21 +1217,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>400022</v>
       </c>
-      <c r="B23" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
       </c>
       <c r="D23">
         <v>110507</v>
       </c>
-      <c r="E23" t="str">
-        <v>铜手镯</v>
+      <c r="E23" t="s">
+        <v>33</v>
       </c>
       <c r="F23">
         <v>20</v>
@@ -1007,21 +1243,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>400023</v>
       </c>
-      <c r="B24" t="str">
-        <v>T004</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
       </c>
       <c r="D24">
         <v>110508</v>
       </c>
-      <c r="E24" t="str">
-        <v>铜戒指</v>
+      <c r="E24" t="s">
+        <v>34</v>
       </c>
       <c r="F24">
         <v>20</v>
@@ -1033,21 +1269,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>400024</v>
       </c>
-      <c r="B25" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C25" t="str">
-        <v>LootTable - 铁掉落池</v>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
       </c>
       <c r="D25">
         <v>130005</v>
       </c>
-      <c r="E25" t="str">
-        <v>铁矿石</v>
+      <c r="E25" t="s">
+        <v>37</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -1058,22 +1294,25 @@
       <c r="H25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="I25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>400025</v>
       </c>
-      <c r="B26" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
       </c>
       <c r="D26">
         <v>110104</v>
       </c>
-      <c r="E26" t="str">
-        <v>铁盔</v>
+      <c r="E26" t="s">
+        <v>38</v>
       </c>
       <c r="F26">
         <v>20</v>
@@ -1085,21 +1324,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>400026</v>
       </c>
-      <c r="B27" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C27" t="str">
-        <v/>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
       </c>
       <c r="D27">
         <v>110204</v>
       </c>
-      <c r="E27" t="str">
-        <v>铁甲</v>
+      <c r="E27" t="s">
+        <v>39</v>
       </c>
       <c r="F27">
         <v>20</v>
@@ -1111,21 +1350,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>400027</v>
       </c>
-      <c r="B28" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C28" t="str">
-        <v/>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
       </c>
       <c r="D28">
         <v>110304</v>
       </c>
-      <c r="E28" t="str">
-        <v>铁靴</v>
+      <c r="E28" t="s">
+        <v>40</v>
       </c>
       <c r="F28">
         <v>20</v>
@@ -1137,21 +1376,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>400028</v>
       </c>
-      <c r="B29" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C29" t="str">
-        <v/>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
       </c>
       <c r="D29">
         <v>110404</v>
       </c>
-      <c r="E29" t="str">
-        <v>铁手套</v>
+      <c r="E29" t="s">
+        <v>41</v>
       </c>
       <c r="F29">
         <v>20</v>
@@ -1163,21 +1402,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>400029</v>
       </c>
-      <c r="B30" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C30" t="str">
-        <v/>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
       </c>
       <c r="D30">
         <v>100104</v>
       </c>
-      <c r="E30" t="str">
-        <v>铁剑</v>
+      <c r="E30" t="s">
+        <v>42</v>
       </c>
       <c r="F30">
         <v>20</v>
@@ -1189,21 +1428,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>400030</v>
       </c>
-      <c r="B31" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C31" t="str">
-        <v/>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
       </c>
       <c r="D31">
         <v>110509</v>
       </c>
-      <c r="E31" t="str">
-        <v>铁项链</v>
+      <c r="E31" t="s">
+        <v>43</v>
       </c>
       <c r="F31">
         <v>15</v>
@@ -1215,21 +1454,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>400031</v>
       </c>
-      <c r="B32" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C32" t="str">
-        <v/>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
       </c>
       <c r="D32">
         <v>110510</v>
       </c>
-      <c r="E32" t="str">
-        <v>铁手镯</v>
+      <c r="E32" t="s">
+        <v>44</v>
       </c>
       <c r="F32">
         <v>15</v>
@@ -1241,21 +1480,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>400032</v>
       </c>
-      <c r="B33" t="str">
-        <v>T005</v>
-      </c>
-      <c r="C33" t="str">
-        <v/>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
       </c>
       <c r="D33">
         <v>110511</v>
       </c>
-      <c r="E33" t="str">
-        <v>铁戒指</v>
+      <c r="E33" t="s">
+        <v>45</v>
       </c>
       <c r="F33">
         <v>15</v>
@@ -1267,21 +1506,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>400033</v>
       </c>
-      <c r="B34" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C34" t="str">
-        <v>LootTable - 金掉落池</v>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
       </c>
       <c r="D34">
         <v>130006</v>
       </c>
-      <c r="E34" t="str">
-        <v>金矿石</v>
+      <c r="E34" t="s">
+        <v>48</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -1292,22 +1531,25 @@
       <c r="H34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="I34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>400034</v>
       </c>
-      <c r="B35" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C35" t="str">
-        <v/>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
       </c>
       <c r="D35">
         <v>110105</v>
       </c>
-      <c r="E35" t="str">
-        <v>金盔</v>
+      <c r="E35" t="s">
+        <v>49</v>
       </c>
       <c r="F35">
         <v>20</v>
@@ -1319,21 +1561,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>400035</v>
       </c>
-      <c r="B36" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C36" t="str">
-        <v/>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
       </c>
       <c r="D36">
         <v>110205</v>
       </c>
-      <c r="E36" t="str">
-        <v>金甲</v>
+      <c r="E36" t="s">
+        <v>50</v>
       </c>
       <c r="F36">
         <v>20</v>
@@ -1345,21 +1587,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>400036</v>
       </c>
-      <c r="B37" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C37" t="str">
-        <v/>
+      <c r="B37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
       </c>
       <c r="D37">
         <v>110305</v>
       </c>
-      <c r="E37" t="str">
-        <v>金靴</v>
+      <c r="E37" t="s">
+        <v>51</v>
       </c>
       <c r="F37">
         <v>20</v>
@@ -1371,21 +1613,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>400037</v>
       </c>
-      <c r="B38" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C38" t="str">
-        <v/>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
       </c>
       <c r="D38">
         <v>110405</v>
       </c>
-      <c r="E38" t="str">
-        <v>金手套</v>
+      <c r="E38" t="s">
+        <v>52</v>
       </c>
       <c r="F38">
         <v>20</v>
@@ -1397,21 +1639,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>400038</v>
       </c>
-      <c r="B39" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C39" t="str">
-        <v/>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
       </c>
       <c r="D39">
         <v>100105</v>
       </c>
-      <c r="E39" t="str">
-        <v>金剑</v>
+      <c r="E39" t="s">
+        <v>53</v>
       </c>
       <c r="F39">
         <v>20</v>
@@ -1423,21 +1665,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>400039</v>
       </c>
-      <c r="B40" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C40" t="str">
-        <v/>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
       </c>
       <c r="D40">
         <v>110512</v>
       </c>
-      <c r="E40" t="str">
-        <v>金项链</v>
+      <c r="E40" t="s">
+        <v>54</v>
       </c>
       <c r="F40">
         <v>15</v>
@@ -1449,21 +1691,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>400040</v>
       </c>
-      <c r="B41" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C41" t="str">
-        <v/>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
       </c>
       <c r="D41">
         <v>110513</v>
       </c>
-      <c r="E41" t="str">
-        <v>金手镯</v>
+      <c r="E41" t="s">
+        <v>55</v>
       </c>
       <c r="F41">
         <v>15</v>
@@ -1475,21 +1717,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>400041</v>
       </c>
-      <c r="B42" t="str">
-        <v>T006</v>
-      </c>
-      <c r="C42" t="str">
-        <v/>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
       </c>
       <c r="D42">
         <v>110514</v>
       </c>
-      <c r="E42" t="str">
-        <v>金戒指</v>
+      <c r="E42" t="s">
+        <v>56</v>
       </c>
       <c r="F42">
         <v>15</v>
@@ -1501,21 +1743,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>400042</v>
       </c>
-      <c r="B43" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C43" t="str">
-        <v>LootTable - 钻石掉落池</v>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="s">
+        <v>58</v>
       </c>
       <c r="D43">
         <v>130007</v>
       </c>
-      <c r="E43" t="str">
-        <v>钻石</v>
+      <c r="E43" t="s">
+        <v>59</v>
       </c>
       <c r="F43">
         <v>80</v>
@@ -1526,22 +1768,25 @@
       <c r="H43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="I43">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>400043</v>
       </c>
-      <c r="B44" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C44" t="str">
-        <v/>
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
       </c>
       <c r="D44">
         <v>110106</v>
       </c>
-      <c r="E44" t="str">
-        <v>钻石盔</v>
+      <c r="E44" t="s">
+        <v>60</v>
       </c>
       <c r="F44">
         <v>15</v>
@@ -1553,21 +1798,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>400044</v>
       </c>
-      <c r="B45" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C45" t="str">
-        <v/>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
       </c>
       <c r="D45">
         <v>110206</v>
       </c>
-      <c r="E45" t="str">
-        <v>钻石甲</v>
+      <c r="E45" t="s">
+        <v>61</v>
       </c>
       <c r="F45">
         <v>15</v>
@@ -1579,21 +1824,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>400045</v>
       </c>
-      <c r="B46" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C46" t="str">
-        <v/>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
       </c>
       <c r="D46">
         <v>110306</v>
       </c>
-      <c r="E46" t="str">
-        <v>钻石靴</v>
+      <c r="E46" t="s">
+        <v>62</v>
       </c>
       <c r="F46">
         <v>15</v>
@@ -1605,21 +1850,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>400046</v>
       </c>
-      <c r="B47" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C47" t="str">
-        <v/>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
       </c>
       <c r="D47">
         <v>110406</v>
       </c>
-      <c r="E47" t="str">
-        <v>钻石手套</v>
+      <c r="E47" t="s">
+        <v>63</v>
       </c>
       <c r="F47">
         <v>15</v>
@@ -1631,21 +1876,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>400047</v>
       </c>
-      <c r="B48" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C48" t="str">
-        <v/>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
       </c>
       <c r="D48">
         <v>100106</v>
       </c>
-      <c r="E48" t="str">
-        <v>钻石剑</v>
+      <c r="E48" t="s">
+        <v>64</v>
       </c>
       <c r="F48">
         <v>15</v>
@@ -1657,21 +1902,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>400048</v>
       </c>
-      <c r="B49" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C49" t="str">
-        <v/>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
       </c>
       <c r="D49">
         <v>110515</v>
       </c>
-      <c r="E49" t="str">
-        <v>钻石项链</v>
+      <c r="E49" t="s">
+        <v>65</v>
       </c>
       <c r="F49">
         <v>10</v>
@@ -1683,21 +1928,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>400049</v>
       </c>
-      <c r="B50" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C50" t="str">
-        <v/>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
       </c>
       <c r="D50">
         <v>110516</v>
       </c>
-      <c r="E50" t="str">
-        <v>钻石手镯</v>
+      <c r="E50" t="s">
+        <v>66</v>
       </c>
       <c r="F50">
         <v>10</v>
@@ -1709,21 +1954,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>400050</v>
       </c>
-      <c r="B51" t="str">
-        <v>T007</v>
-      </c>
-      <c r="C51" t="str">
-        <v/>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
       </c>
       <c r="D51">
         <v>110517</v>
       </c>
-      <c r="E51" t="str">
-        <v>钻石戒指</v>
+      <c r="E51" t="s">
+        <v>67</v>
       </c>
       <c r="F51">
         <v>10</v>
@@ -1735,21 +1980,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>400051</v>
       </c>
-      <c r="B52" t="str">
-        <v>T008</v>
-      </c>
-      <c r="C52" t="str">
-        <v>LootTable - 传说掉落池</v>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
       </c>
       <c r="D52">
         <v>100107</v>
       </c>
-      <c r="E52" t="str">
-        <v>传说之刃</v>
+      <c r="E52" t="s">
+        <v>70</v>
       </c>
       <c r="F52">
         <v>3</v>
@@ -1760,22 +2005,25 @@
       <c r="H52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="I52">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>400052</v>
       </c>
-      <c r="B53" t="str">
-        <v>T008</v>
-      </c>
-      <c r="C53" t="str">
-        <v/>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
       </c>
       <c r="D53">
         <v>110207</v>
       </c>
-      <c r="E53" t="str">
-        <v>远古龙鳞甲</v>
+      <c r="E53" t="s">
+        <v>71</v>
       </c>
       <c r="F53">
         <v>3</v>
@@ -1788,8 +2036,10 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H53"/>
+    <ignoredError sqref="A1:H53" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>